--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/02_FR2 - Eskalasyon ve Müşteri Koruma/EKG-KLT-FRM-36_musteri_koruma_temiz__kirli_sinir_ve_ilk_sertifikali_se.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/02_FR2 - Eskalasyon ve Müşteri Koruma/EKG-KLT-FRM-36_musteri_koruma_temiz__kirli_sinir_ve_ilk_sertifikali_se.xlsx
@@ -986,7 +986,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-36&amp;C&amp;"Arial,Regular"&amp;11Müşteri Koruma, Temiz / Kirli Sınır ve İlk Sertifikalı Sevkiyat Bildirim Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Koruma ve müşteri onay akışı korundu; miktar denkliğine tam sayı/negatif giriş denetimi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bbf3c9ce7134526"/>
   <x:tableParts count="1">
@@ -1328,7 +1329,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-36&amp;C&amp;"Arial,Regular"&amp;11Müşteri Koruma, Temiz / Kirli Sınır ve İlk Sertifikalı Sevkiyat Bildirim Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Koruma ve müşteri onay akışı korundu; miktar denkliğine tam sayı/negatif giriş denetimi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re738e48bf2594ea4"/>
   <x:tableParts count="1">
@@ -1673,7 +1675,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-36&amp;C&amp;"Arial,Regular"&amp;11Müşteri Koruma, Temiz / Kirli Sınır ve İlk Sertifikalı Sevkiyat Bildirim Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Koruma ve müşteri onay akışı korundu; miktar denkliğine tam sayı/negatif giriş denetimi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c6235e6edf84480"/>
   <x:tableParts count="1">
@@ -1978,7 +1981,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-36&amp;C&amp;"Arial,Regular"&amp;11Müşteri Koruma, Temiz / Kirli Sınır ve İlk Sertifikalı Sevkiyat Bildirim Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Koruma ve müşteri onay akışı korundu; miktar denkliğine tam sayı/negatif giriş denetimi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64dab952bb0d4893"/>
   <x:tableParts count="1">
@@ -2218,7 +2222,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-36&amp;C&amp;"Arial,Regular"&amp;11Müşteri Koruma, Temiz / Kirli Sınır ve İlk Sertifikalı Sevkiyat Bildirim Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Koruma ve müşteri onay akışı korundu; miktar denkliğine tam sayı/negatif giriş denetimi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c26e9c02a194741"/>
   <x:tableParts count="1">
